--- a/results/Int All Data 1.0/Linea_1_permute.xlsx
+++ b/results/Int All Data 1.0/Linea_1_permute.xlsx
@@ -446,147 +446,147 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5297356828193832</v>
+        <v>0.5542515747088668</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5297356828193832</v>
+        <v>0.5552192340036869</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5275330396475771</v>
+        <v>0.5473568281938326</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5275330396475771</v>
+        <v>0.5473568281938326</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5275330396475771</v>
+        <v>0.5440528634361234</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.512114537444934</v>
+        <v>0.5462555066079295</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5162037681627561</v>
+        <v>0.5462555066079295</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.515102446576853</v>
+        <v>0.5330396475770925</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.515102446576853</v>
+        <v>0.5319383259911894</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5</v>
+        <v>0.5242290748898678</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5</v>
+        <v>0.5242290748898678</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5</v>
+        <v>0.525330396475771</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5</v>
+        <v>0.5242290748898678</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5</v>
+        <v>0.5275330396475771</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -596,7 +596,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -606,7 +606,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -616,7 +616,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -626,7 +626,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -636,7 +636,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -646,7 +646,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -656,7 +656,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -666,7 +666,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -676,7 +676,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -686,7 +686,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -696,7 +696,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -706,7 +706,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -716,7 +716,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -726,7 +726,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -736,7 +736,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -746,7 +746,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -756,7 +756,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -766,7 +766,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -776,7 +776,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -796,7 +796,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -806,7 +806,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -816,7 +816,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -826,7 +826,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -836,7 +836,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -846,7 +846,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -856,7 +856,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -866,7 +866,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -876,7 +876,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -886,7 +886,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -896,7 +896,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -906,7 +906,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -916,7 +916,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -926,7 +926,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -936,7 +936,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -946,7 +946,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -956,7 +956,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -966,7 +966,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -976,7 +976,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -986,7 +986,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -996,7 +996,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1006,7 +1006,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1016,7 +1016,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1026,7 +1026,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1036,7 +1036,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1046,7 +1046,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1056,7 +1056,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1066,7 +1066,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1076,7 +1076,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1086,7 +1086,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1096,7 +1096,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1106,7 +1106,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1116,7 +1116,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1126,7 +1126,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1136,7 +1136,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1146,7 +1146,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1156,7 +1156,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1166,7 +1166,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1176,7 +1176,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1186,11 +1186,11 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5</v>
+        <v>0.6324467996235179</v>
       </c>
     </row>
     <row r="78">
@@ -1200,693 +1200,693 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5</v>
+        <v>0.6314986327461475</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5</v>
+        <v>0.6321307439977277</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5</v>
+        <v>0.6324467996235179</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>0.6324467996235179</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5</v>
+        <v>0.6316030564110562</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.6316030564110562</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.6316030564110562</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5</v>
+        <v>0.6322644062888108</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5</v>
+        <v>0.6322644062888108</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.6322644062888108</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.6322644062888108</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.6322644062888108</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.6331930807487316</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5</v>
+        <v>0.6342944023346346</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5</v>
+        <v>0.6316225488285057</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5</v>
+        <v>0.6327238704144087</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5</v>
+        <v>0.6327238704144087</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5</v>
+        <v>0.6327238704144087</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5</v>
+        <v>0.6327238704144087</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5</v>
+        <v>0.6327238704144087</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5</v>
+        <v>0.6316225488285057</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5</v>
+        <v>0.6327238704144087</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5</v>
+        <v>0.6327238704144087</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5</v>
+        <v>0.6335091363745218</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5</v>
+        <v>0.6346104579604248</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5</v>
+        <v>0.6346104579604248</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5</v>
+        <v>0.6316225488285057</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5</v>
+        <v>0.6316225488285057</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5</v>
+        <v>0.634926513586215</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5</v>
+        <v>0.634926513586215</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5</v>
+        <v>0.634926513586215</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5</v>
+        <v>0.634926513586215</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5</v>
+        <v>0.634926513586215</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5</v>
+        <v>0.634926513586215</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5</v>
+        <v>0.634926513586215</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5</v>
+        <v>0.634926513586215</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5</v>
+        <v>0.634926513586215</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5</v>
+        <v>0.634926513586215</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5</v>
+        <v>0.6319386044542958</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5</v>
+        <v>0.632254660080086</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5</v>
+        <v>0.6346299503778745</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5</v>
+        <v>0.6346299503778745</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5</v>
+        <v>0.6324273072060682</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5</v>
+        <v>0.6324273072060682</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5</v>
+        <v>0.6324273072060682</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5</v>
+        <v>0.6327433628318584</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5</v>
+        <v>0.6327433628318584</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5</v>
+        <v>0.6324273072060682</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5</v>
+        <v>0.6339978391262941</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5</v>
+        <v>0.6339978391262941</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5</v>
+        <v>0.6339978391262941</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5</v>
+        <v>0.6339978391262941</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5</v>
+        <v>0.6339978391262941</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5</v>
+        <v>0.6339978391262941</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5</v>
+        <v>0.6339978391262941</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5</v>
+        <v>0.6339978391262941</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.633681783500504</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5</v>
+        <v>0.6330496722489238</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5</v>
+        <v>0.6333657278747139</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5</v>
+        <v>0.6333657278747139</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5</v>
+        <v>0.6330496722489238</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5</v>
+        <v>0.6330496722489238</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.6321015053715533</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.6330399260401989</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.6308372828683928</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.6308372828683928</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.6308372828683928</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.6308372828683928</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.6308372828683928</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -1896,7 +1896,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -1906,7 +1906,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1916,7 +1916,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -1926,7 +1926,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -1936,7 +1936,7 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,7 +1946,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B156" t="n">
